--- a/data/trans_dic/IP2906_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida</t>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,71; 52,98</t>
+          <t>35,87; 52,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,11; 37,88</t>
+          <t>21,98; 36,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,34; 41,7</t>
+          <t>30,13; 41,45</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,28; 52,97</t>
+          <t>35,56; 52,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,24; 49,37</t>
+          <t>31,73; 50,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,53; 48,77</t>
+          <t>35,62; 48,25</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 54,06</t>
+          <t>28,8; 52,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,99; 57,79</t>
+          <t>34,97; 58,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,62; 52,74</t>
+          <t>35,82; 52,69</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,54; 47,95</t>
+          <t>34,76; 47,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,06; 53,97</t>
+          <t>39,4; 53,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,07; 48,69</t>
+          <t>39,22; 49,15</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,94; 54,21</t>
+          <t>37,49; 53,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,64; 50,52</t>
+          <t>32,88; 51,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,0; 49,3</t>
+          <t>36,72; 49,68</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,61; 56,1</t>
+          <t>34,07; 55,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,17; 66,11</t>
+          <t>44,11; 66,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,83; 57,67</t>
+          <t>42,53; 57,69</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,78; 47,04</t>
+          <t>39,93; 47,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,7; 46,17</t>
+          <t>38,93; 46,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,38; 45,57</t>
+          <t>40,51; 45,58</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>44613</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38844</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83457</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>35925; 52889</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29161; 48734</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>70144; 96492</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>40995</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37761</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78756</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>33209; 48941</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29589; 46621</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66474; 90059</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>20198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29049</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49247</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13953; 25496</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21800; 36402</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39680; 58368</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>77049</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>97424</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>174473</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>64520; 89013</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>83106; 113792</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>155493; 194874</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>51799</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67736</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>119535</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>43039; 61773</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52426; 81609</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>100715; 136251</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>30090</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37782</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>67872</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>22962; 37218</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30022; 45087</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57615; 78144</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>264745</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>308595</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>573341</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>243478; 288152</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>282923; 337371</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>541388; 609099</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2906_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,87; 52,82</t>
+          <t>34,94; 53,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,98; 36,73</t>
+          <t>22,3; 36,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,13; 41,45</t>
+          <t>30,43; 41,7</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,56; 52,4</t>
+          <t>35,9; 52,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 50,0</t>
+          <t>32,17; 49,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,62; 48,25</t>
+          <t>35,82; 48,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,8; 52,62</t>
+          <t>30,72; 54,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,97; 58,4</t>
+          <t>34,85; 58,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,82; 52,69</t>
+          <t>36,25; 53,1</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 47,96</t>
+          <t>35,09; 48,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,4; 53,95</t>
+          <t>39,44; 52,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,22; 49,15</t>
+          <t>38,96; 49,11</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,49; 53,81</t>
+          <t>36,06; 53,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,88; 51,18</t>
+          <t>32,72; 50,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,72; 49,68</t>
+          <t>36,67; 49,57</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,07; 55,23</t>
+          <t>34,78; 56,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,11; 66,24</t>
+          <t>43,74; 66,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,53; 57,69</t>
+          <t>42,17; 57,72</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,93; 47,26</t>
+          <t>40,0; 47,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,93; 46,43</t>
+          <t>38,66; 46,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,51; 45,58</t>
+          <t>40,29; 45,29</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35925; 52889</t>
+          <t>34994; 53129</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29161; 48734</t>
+          <t>29581; 48766</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70144; 96492</t>
+          <t>70843; 97076</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33209; 48941</t>
+          <t>33526; 48658</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29589; 46621</t>
+          <t>29997; 46064</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66474; 90059</t>
+          <t>66859; 89974</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13953; 25496</t>
+          <t>14882; 26169</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21800; 36402</t>
+          <t>21723; 36579</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39680; 58368</t>
+          <t>40160; 58825</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64520; 89013</t>
+          <t>65119; 89304</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83106; 113792</t>
+          <t>83181; 111596</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>155493; 194874</t>
+          <t>154465; 194712</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43039; 61773</t>
+          <t>41392; 61264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52426; 81609</t>
+          <t>52172; 80031</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100715; 136251</t>
+          <t>100578; 135954</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22962; 37218</t>
+          <t>23440; 38040</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30022; 45087</t>
+          <t>29772; 45394</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57615; 78144</t>
+          <t>57122; 78182</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>243478; 288152</t>
+          <t>243883; 287020</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282923; 337371</t>
+          <t>280907; 336297</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>541388; 609099</t>
+          <t>538490; 605228</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,94; 53,05</t>
+          <t>24,49; 39,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,3; 36,76</t>
+          <t>36,93; 53,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 41,7</t>
+          <t>32,02; 42,72</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,9; 52,1</t>
+          <t>31,03; 49,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,17; 49,4</t>
+          <t>35,01; 52,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,82; 48,21</t>
+          <t>36,09; 48,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,72; 54,01</t>
+          <t>35,54; 58,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,85; 58,68</t>
+          <t>32,15; 56,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,25; 53,1</t>
+          <t>37,94; 54,12</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,09; 48,12</t>
+          <t>39,25; 54,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,44; 52,91</t>
+          <t>36,69; 49,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,96; 49,11</t>
+          <t>40,23; 49,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,06; 53,37</t>
+          <t>34,31; 52,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 50,19</t>
+          <t>35,91; 51,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,67; 49,57</t>
+          <t>38,03; 49,59</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,78; 56,45</t>
+          <t>45,78; 68,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,74; 66,69</t>
+          <t>35,74; 57,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,17; 57,72</t>
+          <t>44,6; 59,49</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,0; 47,07</t>
+          <t>39,9; 47,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,66; 46,28</t>
+          <t>40,35; 47,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,29; 45,29</t>
+          <t>41,28; 46,36</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44613</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>44392</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83457</t>
+          <t>80906</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34994; 53129</t>
+          <t>29093; 47343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29581; 48766</t>
+          <t>36469; 53041</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70843; 97076</t>
+          <t>69666; 92941</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78756</t>
+          <t>77674</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33526; 48658</t>
+          <t>27765; 44366</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29997; 46064</t>
+          <t>33403; 50533</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66859; 89974</t>
+          <t>66717; 90109</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29049</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>48393</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14882; 26169</t>
+          <t>19847; 32697</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21723; 36579</t>
+          <t>15988; 27998</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40160; 58825</t>
+          <t>40056; 57139</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>77049</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>97424</t>
+          <t>73596</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174473</t>
+          <t>164552</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65119; 89304</t>
+          <t>76774; 105868</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83181; 111596</t>
+          <t>62606; 84089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154465; 194712</t>
+          <t>147347; 181806</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51799</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>49642</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119535</t>
+          <t>114191</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41392; 61264</t>
+          <t>49949; 76764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52172; 80031</t>
+          <t>41162; 59584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100578; 135954</t>
+          <t>98954; 129057</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67872</t>
+          <t>69376</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23440; 38040</t>
+          <t>29716; 44324</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29772; 45394</t>
+          <t>24575; 39763</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57122; 78182</t>
+          <t>59619; 79527</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>396</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>264745</t>
+          <t>292407</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>308595</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>573341</t>
+          <t>555093</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>243883; 287020</t>
+          <t>267384; 316979</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280907; 336297</t>
+          <t>241268; 283763</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>538490; 605228</t>
+          <t>523500; 587930</t>
         </is>
       </c>
     </row>
